--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.035375</v>
+        <v>-0.04765</v>
       </c>
       <c r="E2">
-        <v>0.395</v>
+        <v>0.23415</v>
       </c>
       <c r="F2">
-        <v>0.175</v>
+        <v>0.3995</v>
       </c>
       <c r="G2">
-        <v>0.1416736588510251</v>
+        <v>0.1841780974121735</v>
       </c>
       <c r="H2">
-        <v>0.1416736588510251</v>
+        <v>0.1841780974121735</v>
       </c>
       <c r="I2">
-        <v>0.1202359946113987</v>
+        <v>-0.0210355778657739</v>
       </c>
       <c r="J2">
-        <v>0.1016350944766663</v>
+        <v>-0.020135863390792</v>
       </c>
       <c r="K2">
-        <v>4684.25</v>
+        <v>4358.76</v>
       </c>
       <c r="L2">
-        <v>0.08434284870593572</v>
+        <v>0.2935132623583362</v>
       </c>
       <c r="M2">
-        <v>2972.3434</v>
+        <v>11006.42</v>
       </c>
       <c r="N2">
-        <v>0.05806356170591819</v>
+        <v>0.2636817732078301</v>
       </c>
       <c r="O2">
-        <v>0.6345398729785985</v>
+        <v>2.525126412098854</v>
       </c>
       <c r="P2">
-        <v>1866.2434</v>
+        <v>1388.82</v>
       </c>
       <c r="Q2">
-        <v>0.03645633233837066</v>
+        <v>0.03327208304485006</v>
       </c>
       <c r="R2">
-        <v>0.398408154987458</v>
+        <v>0.3186273160256586</v>
       </c>
       <c r="S2">
-        <v>1106.1</v>
+        <v>9617.6</v>
       </c>
       <c r="T2">
-        <v>0.3721306225922617</v>
+        <v>0.8738172811867982</v>
       </c>
       <c r="U2">
-        <v>17193.6</v>
+        <v>18431.5</v>
       </c>
       <c r="V2">
-        <v>0.3358702276953851</v>
+        <v>0.4415650686490358</v>
       </c>
       <c r="W2">
-        <v>0.03926009993814807</v>
+        <v>0.03021820722284185</v>
       </c>
       <c r="X2">
-        <v>0.05743326515436344</v>
+        <v>0.09362846604833289</v>
       </c>
       <c r="Y2">
-        <v>-0.01817316521621536</v>
+        <v>-0.06341025882549103</v>
       </c>
       <c r="Z2">
-        <v>3.652808463141362</v>
+        <v>0.6176758226703717</v>
       </c>
       <c r="AA2">
-        <v>0.1853177435252384</v>
+        <v>-0.01353116128181721</v>
       </c>
       <c r="AB2">
-        <v>0.04945994222589932</v>
+        <v>0.08088263775415294</v>
       </c>
       <c r="AC2">
-        <v>0.1275602038628754</v>
+        <v>-0.1048156967123811</v>
       </c>
       <c r="AD2">
-        <v>16451.8</v>
+        <v>14319.3</v>
       </c>
       <c r="AE2">
-        <v>1053.496420366093</v>
+        <v>776.323209900511</v>
       </c>
       <c r="AF2">
-        <v>17505.29642036609</v>
+        <v>15095.62320990051</v>
       </c>
       <c r="AG2">
-        <v>311.6964203660937</v>
+        <v>-3335.87679009949</v>
       </c>
       <c r="AH2">
-        <v>0.254820803571234</v>
+        <v>0.2655953622639267</v>
       </c>
       <c r="AI2">
-        <v>0.3106001024173478</v>
+        <v>0.3501309332748</v>
       </c>
       <c r="AJ2">
-        <v>0.006052017304464408</v>
+        <v>-0.08685952428821396</v>
       </c>
       <c r="AK2">
-        <v>0.007958342665935937</v>
+        <v>-0.1351502734010092</v>
       </c>
       <c r="AL2">
-        <v>939.0999999999999</v>
+        <v>710.1</v>
       </c>
       <c r="AM2">
-        <v>939.0999999999999</v>
+        <v>710.1</v>
       </c>
       <c r="AN2">
-        <v>2.101687553494551</v>
+        <v>25.0688025210084</v>
       </c>
       <c r="AO2">
-        <v>7.138100308806304</v>
+        <v>-0.4733417828474862</v>
       </c>
       <c r="AP2">
-        <v>0.03981865128145398</v>
+        <v>-5.840120430846445</v>
       </c>
       <c r="AQ2">
-        <v>7.138100308806304</v>
+        <v>-0.4733417828474862</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Willis Towers Watson Public Limited Company (NasdaqGS:WLTW)</t>
+          <t>Willis Towers Watson Public Limited Company (NasdaqGS:WTW)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0722</v>
+        <v>0.0197</v>
       </c>
       <c r="E3">
-        <v>0.5529999999999999</v>
+        <v>0.417</v>
       </c>
       <c r="F3">
-        <v>0.19</v>
+        <v>0.155</v>
       </c>
       <c r="G3">
-        <v>0.242627345844504</v>
+        <v>0.2614689265536723</v>
       </c>
       <c r="H3">
-        <v>0.242627345844504</v>
+        <v>0.2614689265536723</v>
       </c>
       <c r="I3">
-        <v>0.2011033940943268</v>
+        <v>0.1965802664429263</v>
       </c>
       <c r="J3">
-        <v>0.1613560635204741</v>
+        <v>0.1629484618225703</v>
       </c>
       <c r="K3">
-        <v>2296</v>
+        <v>2823</v>
       </c>
       <c r="L3">
-        <v>0.2367498453289338</v>
+        <v>0.3189830508474576</v>
       </c>
       <c r="M3">
-        <v>1370</v>
+        <v>4136</v>
       </c>
       <c r="N3">
-        <v>0.04629520118137243</v>
+        <v>0.1562358345169381</v>
       </c>
       <c r="O3">
-        <v>0.5966898954703833</v>
+        <v>1.465108041091038</v>
       </c>
       <c r="P3">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="Q3">
-        <v>0.01223274658953053</v>
+        <v>0.01431658154785289</v>
       </c>
       <c r="R3">
-        <v>0.1576655052264808</v>
+        <v>0.1342543393552958</v>
       </c>
       <c r="S3">
-        <v>1008</v>
+        <v>3757</v>
       </c>
       <c r="T3">
-        <v>0.7357664233576642</v>
+        <v>0.9083655705996132</v>
       </c>
       <c r="U3">
-        <v>2162</v>
+        <v>1496</v>
       </c>
       <c r="V3">
-        <v>0.07305855836067679</v>
+        <v>0.05651083376144571</v>
       </c>
       <c r="W3">
-        <v>0.2183547313361864</v>
+        <v>0.2477837268498201</v>
       </c>
       <c r="X3">
-        <v>0.05326554119982344</v>
+        <v>0.08796278480525423</v>
       </c>
       <c r="Y3">
-        <v>0.165089190136363</v>
+        <v>0.1598209420445658</v>
       </c>
       <c r="Z3">
-        <v>2.201840817750948</v>
+        <v>1.959992582722555</v>
       </c>
       <c r="AA3">
-        <v>0.3552803668509945</v>
+        <v>0.3193777765382871</v>
       </c>
       <c r="AB3">
-        <v>0.04938817278131671</v>
+        <v>0.08135442098838865</v>
       </c>
       <c r="AC3">
-        <v>0.3058921940696777</v>
+        <v>0.2380233555498985</v>
       </c>
       <c r="AD3">
-        <v>4654</v>
+        <v>4733</v>
       </c>
       <c r="AE3">
-        <v>1053.496420366093</v>
+        <v>776.323209900511</v>
       </c>
       <c r="AF3">
-        <v>5707.496420366093</v>
+        <v>5509.323209900511</v>
       </c>
       <c r="AG3">
-        <v>3545.496420366093</v>
+        <v>4013.323209900511</v>
       </c>
       <c r="AH3">
-        <v>0.1616845513378846</v>
+        <v>0.1722625847490646</v>
       </c>
       <c r="AI3">
-        <v>0.3329831459014528</v>
+        <v>0.3572304337626478</v>
       </c>
       <c r="AJ3">
-        <v>0.1069912307655675</v>
+        <v>0.1316442626131343</v>
       </c>
       <c r="AK3">
-        <v>0.2367057627723782</v>
+        <v>0.2881825410347619</v>
       </c>
       <c r="AL3">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="AM3">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="AN3">
-        <v>1.729468599033816</v>
+        <v>1.981163666806195</v>
       </c>
       <c r="AO3">
-        <v>8.941176470588236</v>
+        <v>8.411764705882353</v>
       </c>
       <c r="AP3">
-        <v>1.317538617750313</v>
+        <v>1.679917626580373</v>
       </c>
       <c r="AQ3">
-        <v>8.941176470588236</v>
+        <v>8.411764705882353</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aviva plc (LSE:AV.)</t>
+          <t>Saga plc (LSE:SAGA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,124 +862,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00145</v>
-      </c>
-      <c r="E4">
-        <v>0.237</v>
-      </c>
-      <c r="F4">
-        <v>0.16</v>
+        <v>-0.115</v>
       </c>
       <c r="G4">
-        <v>0.1201169807325852</v>
+        <v>0.1089600822340243</v>
       </c>
       <c r="H4">
-        <v>0.1201169807325852</v>
+        <v>0.1089600822340243</v>
       </c>
       <c r="I4">
-        <v>0.1027749841202625</v>
+        <v>0.0930272400205585</v>
       </c>
       <c r="J4">
-        <v>0.05948957407516201</v>
+        <v>0.0930272400205585</v>
       </c>
       <c r="K4">
-        <v>2410.1</v>
+        <v>-350.4</v>
       </c>
       <c r="L4">
-        <v>0.05315521561154633</v>
+        <v>-0.6003083775912282</v>
       </c>
       <c r="M4">
-        <v>1599.4</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.07651935948406603</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.6636239160200821</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1501.3</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.0718260062482358</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.6229202107796357</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>98.09999999999991</v>
-      </c>
-      <c r="T4">
-        <v>0.06133550081280475</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>14714.5</v>
+        <v>218.8</v>
       </c>
       <c r="V4">
-        <v>0.7039790641042202</v>
+        <v>1.028678890456042</v>
       </c>
       <c r="W4">
-        <v>0.1047855897531771</v>
+        <v>-0.3665655403284862</v>
       </c>
       <c r="X4">
-        <v>0.06160098910890344</v>
+        <v>0.2568094031591843</v>
       </c>
       <c r="Y4">
-        <v>0.04318460064427369</v>
+        <v>-0.6233749434876705</v>
       </c>
       <c r="Z4">
-        <v>4.489321464994013</v>
+        <v>0.6068198357417612</v>
       </c>
       <c r="AA4">
-        <v>0.2670678218389761</v>
+        <v>0.0564507745087847</v>
       </c>
       <c r="AB4">
-        <v>0.04953171167048193</v>
+        <v>0.1021582163412106</v>
       </c>
       <c r="AC4">
-        <v>0.2175361101684942</v>
+        <v>-0.04570744183242592</v>
       </c>
       <c r="AD4">
-        <v>10547.6</v>
+        <v>1170.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10547.6</v>
+        <v>1170.3</v>
       </c>
       <c r="AG4">
-        <v>-4166.9</v>
+        <v>951.5</v>
       </c>
       <c r="AH4">
-        <v>0.335382120542457</v>
+        <v>0.8462039045553145</v>
       </c>
       <c r="AI4">
-        <v>0.2860296291073574</v>
+        <v>0.7079854809437386</v>
       </c>
       <c r="AJ4">
-        <v>-0.2489931281744846</v>
+        <v>0.8172994330870984</v>
       </c>
       <c r="AK4">
-        <v>-0.1880251247664858</v>
+        <v>0.6634360619160508</v>
       </c>
       <c r="AL4">
-        <v>664.3</v>
+        <v>50.4</v>
       </c>
       <c r="AM4">
-        <v>664.3</v>
+        <v>50.4</v>
       </c>
       <c r="AN4">
-        <v>2.088302843113962</v>
+        <v>13.56083429895713</v>
       </c>
       <c r="AO4">
-        <v>7.014752370916755</v>
+        <v>1.077380952380952</v>
       </c>
       <c r="AP4">
-        <v>-0.8249980201156252</v>
+        <v>11.02549246813441</v>
       </c>
       <c r="AQ4">
-        <v>7.014752370916755</v>
+        <v>1.077380952380952</v>
       </c>
     </row>
     <row r="5">
@@ -990,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saga plc (LSE:SAGA)</t>
+          <t>Helios Underwriting plc (AIM:HUW)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -999,43 +990,43 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.202</v>
+        <v>0.288</v>
       </c>
       <c r="G5">
-        <v>0.1642110266159696</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.1642110266159696</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.1634980988593156</v>
+        <v>-0.04524207011686144</v>
       </c>
       <c r="J5">
-        <v>0.1634980988593156</v>
+        <v>-0.04524207011686144</v>
       </c>
       <c r="K5">
-        <v>-19.2</v>
+        <v>-2.14</v>
       </c>
       <c r="L5">
-        <v>-0.04562737642585551</v>
+        <v>-0.01786310517529216</v>
       </c>
       <c r="M5">
-        <v>0.139</v>
+        <v>4.92</v>
       </c>
       <c r="N5">
-        <v>0.0002566943674976916</v>
+        <v>0.03277814790139907</v>
       </c>
       <c r="O5">
-        <v>-0.007239583333333334</v>
+        <v>-2.299065420560748</v>
       </c>
       <c r="P5">
-        <v>0.139</v>
+        <v>4.92</v>
       </c>
       <c r="Q5">
-        <v>0.0002566943674976916</v>
+        <v>0.03277814790139907</v>
       </c>
       <c r="R5">
-        <v>-0.007239583333333334</v>
+        <v>-2.299065420560748</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1044,73 +1035,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>244.9</v>
+        <v>15.8</v>
       </c>
       <c r="V5">
-        <v>0.4522622345337027</v>
+        <v>0.1052631578947369</v>
       </c>
       <c r="W5">
-        <v>-0.02626538987688098</v>
+        <v>-0.01560904449307075</v>
       </c>
       <c r="X5">
-        <v>0.1098387165982148</v>
+        <v>0.08519247392634427</v>
       </c>
       <c r="Y5">
-        <v>-0.1361041064750958</v>
+        <v>-0.100801518419415</v>
       </c>
       <c r="Z5">
-        <v>0.6334487430377841</v>
+        <v>1.845916795069338</v>
       </c>
       <c r="AA5">
-        <v>0.1035676652115008</v>
+        <v>-0.08351309707241912</v>
       </c>
       <c r="AB5">
-        <v>0.06598336765424409</v>
+        <v>0.08041085451991724</v>
       </c>
       <c r="AC5">
-        <v>0.03758429755725672</v>
+        <v>-0.1639239515923364</v>
       </c>
       <c r="AD5">
-        <v>1250.2</v>
+        <v>18.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1250.2</v>
+        <v>18.2</v>
       </c>
       <c r="AG5">
-        <v>1005.3</v>
+        <v>2.399999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.6977730646871686</v>
+        <v>0.1081402257872846</v>
       </c>
       <c r="AI5">
-        <v>0.5667014187933458</v>
+        <v>0.1282593375616631</v>
       </c>
       <c r="AJ5">
-        <v>0.649922420480993</v>
+        <v>0.01573770491803278</v>
       </c>
       <c r="AK5">
-        <v>0.5125943300020396</v>
+        <v>0.01903251387787469</v>
       </c>
       <c r="AL5">
-        <v>53.8</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>53.8</v>
-      </c>
-      <c r="AN5">
-        <v>14.52032520325203</v>
-      </c>
-      <c r="AO5">
-        <v>1.278810408921933</v>
-      </c>
-      <c r="AP5">
-        <v>11.67595818815331</v>
-      </c>
-      <c r="AQ5">
-        <v>1.278810408921933</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Helios Underwriting Plc (AIM:HUW)</t>
+          <t>Aviva plc (LSE:AV.)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1130,106 +1109,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.229</v>
+        <v>-0.344</v>
+      </c>
+      <c r="E6">
+        <v>0.0513</v>
+      </c>
+      <c r="F6">
+        <v>0.644</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>0.06749358103005589</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.06749358103005589</v>
       </c>
       <c r="I6">
-        <v>-0.01666666666666667</v>
+        <v>-0.396654583899713</v>
       </c>
       <c r="J6">
-        <v>-0.01666666666666667</v>
+        <v>-0.396654583899713</v>
       </c>
       <c r="K6">
-        <v>-2.65</v>
+        <v>1888.3</v>
       </c>
       <c r="L6">
-        <v>-0.03371501272264631</v>
+        <v>0.3564982631022504</v>
       </c>
       <c r="M6">
-        <v>2.8044</v>
+        <v>6865.5</v>
       </c>
       <c r="N6">
-        <v>0.01808123791102515</v>
+        <v>0.4605956110749579</v>
       </c>
       <c r="O6">
-        <v>-1.058264150943396</v>
+        <v>3.635809987819732</v>
       </c>
       <c r="P6">
-        <v>2.8044</v>
+        <v>1004.9</v>
       </c>
       <c r="Q6">
-        <v>0.01808123791102515</v>
+        <v>0.06741716256197293</v>
       </c>
       <c r="R6">
-        <v>-1.058264150943396</v>
+        <v>0.532171794736006</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>5860.6</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.8536304711965625</v>
       </c>
       <c r="U6">
-        <v>72.2</v>
+        <v>16700.9</v>
       </c>
       <c r="V6">
-        <v>0.4655061250805932</v>
+        <v>1.120437148205049</v>
       </c>
       <c r="W6">
-        <v>-0.07636887608069164</v>
+        <v>0.07604545893875446</v>
       </c>
       <c r="X6">
-        <v>0.04810879511784055</v>
+        <v>0.09929414729141153</v>
       </c>
       <c r="Y6">
-        <v>-0.1244776711985322</v>
+        <v>-0.02324868835265707</v>
       </c>
       <c r="Z6">
-        <v>2.198601398601399</v>
+        <v>0.2863119658812656</v>
       </c>
       <c r="AA6">
-        <v>-0.03664335664335665</v>
+        <v>-0.1135669536921422</v>
       </c>
       <c r="AB6">
-        <v>0.04810879511784055</v>
+        <v>0.07981867608123741</v>
       </c>
       <c r="AC6">
-        <v>-0.0847521517611972</v>
+        <v>-0.1933856297733796</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>8397.799999999999</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>8397.799999999999</v>
       </c>
       <c r="AG6">
-        <v>-72.2</v>
+        <v>-8303.100000000002</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.3603664685562254</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.3242769432752828</v>
       </c>
       <c r="AJ6">
-        <v>-0.8709288299155611</v>
+        <v>-1.257550056038531</v>
       </c>
       <c r="AK6">
-        <v>-1.112480739599384</v>
+        <v>-0.9028936179467387</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>455.7</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>455.7</v>
+      </c>
+      <c r="AN6">
+        <v>-4.410377606218161</v>
+      </c>
+      <c r="AO6">
+        <v>-4.610489357033136</v>
+      </c>
+      <c r="AP6">
+        <v>4.360642823381126</v>
+      </c>
+      <c r="AQ6">
+        <v>-4.610489357033136</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.04765</v>
+        <v>0.0248</v>
       </c>
       <c r="E2">
-        <v>0.23415</v>
+        <v>0.127</v>
       </c>
       <c r="F2">
-        <v>0.3995</v>
+        <v>0.098</v>
       </c>
       <c r="G2">
-        <v>0.1841780974121735</v>
+        <v>0.06021565742604924</v>
       </c>
       <c r="H2">
-        <v>0.1841780974121735</v>
+        <v>0.06021565742604924</v>
       </c>
       <c r="I2">
-        <v>-0.0210355778657739</v>
+        <v>0.1133332133786206</v>
       </c>
       <c r="J2">
-        <v>-0.020135863390792</v>
+        <v>0.1082301125412904</v>
       </c>
       <c r="K2">
-        <v>4358.76</v>
+        <v>200.54</v>
       </c>
       <c r="L2">
-        <v>0.2935132623583362</v>
+        <v>0.01941110422796965</v>
       </c>
       <c r="M2">
-        <v>11006.42</v>
+        <v>3186.9234</v>
       </c>
       <c r="N2">
-        <v>0.2636817732078301</v>
+        <v>0.07893895273952245</v>
       </c>
       <c r="O2">
-        <v>2.525126412098854</v>
+        <v>15.89170938466141</v>
       </c>
       <c r="P2">
-        <v>1388.82</v>
+        <v>1496.7234</v>
       </c>
       <c r="Q2">
-        <v>0.03327208304485006</v>
+        <v>0.03707330327950065</v>
       </c>
       <c r="R2">
-        <v>0.3186273160256586</v>
+        <v>7.463465642764535</v>
       </c>
       <c r="S2">
-        <v>9617.6</v>
+        <v>1690.2</v>
       </c>
       <c r="T2">
-        <v>0.8738172811867982</v>
+        <v>0.5303547615860488</v>
       </c>
       <c r="U2">
-        <v>18431.5</v>
+        <v>26691.59</v>
       </c>
       <c r="V2">
-        <v>0.4415650686490358</v>
+        <v>0.6611411374219757</v>
       </c>
       <c r="W2">
-        <v>0.03021820722284185</v>
+        <v>-0.001153132399968521</v>
       </c>
       <c r="X2">
-        <v>0.09362846604833289</v>
+        <v>0.08299400786832897</v>
       </c>
       <c r="Y2">
-        <v>-0.06341025882549103</v>
+        <v>-0.08414714026829749</v>
       </c>
       <c r="Z2">
-        <v>0.6176758226703717</v>
+        <v>0.903502648967011</v>
       </c>
       <c r="AA2">
-        <v>-0.01353116128181721</v>
+        <v>0.064807922920321</v>
       </c>
       <c r="AB2">
-        <v>0.08088263775415294</v>
+        <v>0.07244336912586012</v>
       </c>
       <c r="AC2">
-        <v>-0.1048156967123811</v>
+        <v>-0.01843835534510071</v>
       </c>
       <c r="AD2">
-        <v>14319.3</v>
+        <v>14683.4</v>
       </c>
       <c r="AE2">
-        <v>776.323209900511</v>
+        <v>670.7095297139741</v>
       </c>
       <c r="AF2">
-        <v>15095.62320990051</v>
+        <v>15354.10952971397</v>
       </c>
       <c r="AG2">
-        <v>-3335.87679009949</v>
+        <v>-11337.48047028603</v>
       </c>
       <c r="AH2">
-        <v>0.2655953622639267</v>
+        <v>0.2755281080859761</v>
       </c>
       <c r="AI2">
-        <v>0.3501309332748</v>
+        <v>0.4070018913529887</v>
       </c>
       <c r="AJ2">
-        <v>-0.08685952428821396</v>
+        <v>-0.3904827995752859</v>
       </c>
       <c r="AK2">
-        <v>-0.1351502734010092</v>
+        <v>-1.027567491338659</v>
       </c>
       <c r="AL2">
-        <v>710.1</v>
+        <v>765.63</v>
       </c>
       <c r="AM2">
-        <v>710.1</v>
+        <v>765.63</v>
       </c>
       <c r="AN2">
-        <v>25.0688025210084</v>
+        <v>7.222528283325136</v>
       </c>
       <c r="AO2">
-        <v>-0.4733417828474862</v>
+        <v>1.511186865718428</v>
       </c>
       <c r="AP2">
-        <v>-5.840120430846445</v>
+        <v>-5.576724284449594</v>
       </c>
       <c r="AQ2">
-        <v>-0.4733417828474862</v>
+        <v>1.511186865718428</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0197</v>
+        <v>0.0248</v>
       </c>
       <c r="E3">
-        <v>0.417</v>
+        <v>0.127</v>
       </c>
       <c r="F3">
-        <v>0.155</v>
+        <v>0.112</v>
       </c>
       <c r="G3">
-        <v>0.2614689265536723</v>
+        <v>0.2438919384350447</v>
       </c>
       <c r="H3">
-        <v>0.2614689265536723</v>
+        <v>0.2438919384350447</v>
       </c>
       <c r="I3">
-        <v>0.1965802664429263</v>
+        <v>0.2257946500976434</v>
       </c>
       <c r="J3">
-        <v>0.1629484618225703</v>
+        <v>0.1851268587723044</v>
       </c>
       <c r="K3">
-        <v>2823</v>
+        <v>1021</v>
       </c>
       <c r="L3">
-        <v>0.3189830508474576</v>
+        <v>0.1098912926487999</v>
       </c>
       <c r="M3">
-        <v>4136</v>
+        <v>1621</v>
       </c>
       <c r="N3">
-        <v>0.1562358345169381</v>
+        <v>0.06508367327273311</v>
       </c>
       <c r="O3">
-        <v>1.465108041091038</v>
+        <v>1.587659157688541</v>
       </c>
       <c r="P3">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="Q3">
-        <v>0.01431658154785289</v>
+        <v>0.01421321427424276</v>
       </c>
       <c r="R3">
-        <v>0.1342543393552958</v>
+        <v>0.346718903036239</v>
       </c>
       <c r="S3">
-        <v>3757</v>
+        <v>1267</v>
       </c>
       <c r="T3">
-        <v>0.9083655705996132</v>
+        <v>0.7816162862430598</v>
       </c>
       <c r="U3">
-        <v>1496</v>
+        <v>1247</v>
       </c>
       <c r="V3">
-        <v>0.05651083376144571</v>
+        <v>0.05006745254231844</v>
       </c>
       <c r="W3">
-        <v>0.2477837268498201</v>
+        <v>0.1037812563529173</v>
       </c>
       <c r="X3">
-        <v>0.08796278480525423</v>
+        <v>0.07893999843539458</v>
       </c>
       <c r="Y3">
-        <v>0.1598209420445658</v>
+        <v>0.02484125791752267</v>
       </c>
       <c r="Z3">
-        <v>1.959992582722555</v>
+        <v>2.540808867781942</v>
       </c>
       <c r="AA3">
-        <v>0.3193777765382871</v>
+        <v>0.4703719644332862</v>
       </c>
       <c r="AB3">
-        <v>0.08135442098838865</v>
+        <v>0.07226257347224871</v>
       </c>
       <c r="AC3">
-        <v>0.2380233555498985</v>
+        <v>0.3981093909610375</v>
       </c>
       <c r="AD3">
-        <v>4733</v>
+        <v>5222</v>
       </c>
       <c r="AE3">
-        <v>776.323209900511</v>
+        <v>670.7095297139741</v>
       </c>
       <c r="AF3">
-        <v>5509.323209900511</v>
+        <v>5892.709529713974</v>
       </c>
       <c r="AG3">
-        <v>4013.323209900511</v>
+        <v>4645.709529713974</v>
       </c>
       <c r="AH3">
-        <v>0.1722625847490646</v>
+        <v>0.1913272695117656</v>
       </c>
       <c r="AI3">
-        <v>0.3572304337626478</v>
+        <v>0.383198129625718</v>
       </c>
       <c r="AJ3">
-        <v>0.1316442626131343</v>
+        <v>0.1572039899568868</v>
       </c>
       <c r="AK3">
-        <v>0.2881825410347619</v>
+        <v>0.3287668973695201</v>
       </c>
       <c r="AL3">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="AM3">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="AN3">
-        <v>1.981163666806195</v>
+        <v>1.922680412371134</v>
       </c>
       <c r="AO3">
-        <v>8.411764705882353</v>
+        <v>9.221238938053098</v>
       </c>
       <c r="AP3">
-        <v>1.679917626580373</v>
+        <v>1.710496881337987</v>
       </c>
       <c r="AQ3">
-        <v>8.411764705882353</v>
+        <v>9.221238938053098</v>
       </c>
     </row>
     <row r="4">
@@ -862,25 +862,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.115</v>
+        <v>-0.0629</v>
       </c>
       <c r="G4">
-        <v>0.1089600822340243</v>
+        <v>0.1344956413449564</v>
       </c>
       <c r="H4">
-        <v>0.1089600822340243</v>
+        <v>0.1344956413449564</v>
       </c>
       <c r="I4">
-        <v>0.0930272400205585</v>
+        <v>0.08792029887920298</v>
       </c>
       <c r="J4">
-        <v>0.0930272400205585</v>
+        <v>0.08792029887920298</v>
       </c>
       <c r="K4">
-        <v>-350.4</v>
+        <v>-82.2</v>
       </c>
       <c r="L4">
-        <v>-0.6003083775912282</v>
+        <v>-0.1023661270236613</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -904,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>218.8</v>
+        <v>234.6</v>
       </c>
       <c r="V4">
-        <v>1.028678890456042</v>
+        <v>0.8909988606152677</v>
       </c>
       <c r="W4">
-        <v>-0.3665655403284862</v>
+        <v>-0.1702921068986948</v>
       </c>
       <c r="X4">
-        <v>0.2568094031591843</v>
+        <v>0.1801542354546815</v>
       </c>
       <c r="Y4">
-        <v>-0.6233749434876705</v>
+        <v>-0.3504463423533763</v>
       </c>
       <c r="Z4">
-        <v>0.6068198357417612</v>
+        <v>0.9050946798917944</v>
       </c>
       <c r="AA4">
-        <v>0.0564507745087847</v>
+        <v>0.07957619477006311</v>
       </c>
       <c r="AB4">
-        <v>0.1021582163412106</v>
+        <v>0.0938683917513719</v>
       </c>
       <c r="AC4">
-        <v>-0.04570744183242592</v>
+        <v>-0.01429219698130879</v>
       </c>
       <c r="AD4">
-        <v>1170.3</v>
+        <v>1104.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1170.3</v>
+        <v>1104.6</v>
       </c>
       <c r="AG4">
-        <v>951.5</v>
+        <v>869.9999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.8462039045553145</v>
+        <v>0.8075151692375174</v>
       </c>
       <c r="AI4">
-        <v>0.7079854809437386</v>
+        <v>0.7448415374241402</v>
       </c>
       <c r="AJ4">
-        <v>0.8172994330870984</v>
+        <v>0.7676696373422747</v>
       </c>
       <c r="AK4">
-        <v>0.6634360619160508</v>
+        <v>0.6968920217878884</v>
       </c>
       <c r="AL4">
-        <v>50.4</v>
+        <v>53.1</v>
       </c>
       <c r="AM4">
-        <v>50.4</v>
+        <v>53.1</v>
       </c>
       <c r="AN4">
-        <v>13.56083429895713</v>
+        <v>10.787109375</v>
       </c>
       <c r="AO4">
-        <v>1.077380952380952</v>
+        <v>1.329566854990584</v>
       </c>
       <c r="AP4">
-        <v>11.02549246813441</v>
+        <v>8.496093749999998</v>
       </c>
       <c r="AQ4">
-        <v>1.077380952380952</v>
+        <v>1.329566854990584</v>
       </c>
     </row>
     <row r="5">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.288</v>
+        <v>0.436</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -999,34 +999,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>-0.04524207011686144</v>
+        <v>0.02660202360876897</v>
       </c>
       <c r="J5">
-        <v>-0.04524207011686144</v>
+        <v>0.02660202360876897</v>
       </c>
       <c r="K5">
-        <v>-2.14</v>
+        <v>5.14</v>
       </c>
       <c r="L5">
-        <v>-0.01786310517529216</v>
+        <v>0.02166947723440135</v>
       </c>
       <c r="M5">
-        <v>4.92</v>
+        <v>2.8234</v>
       </c>
       <c r="N5">
-        <v>0.03277814790139907</v>
+        <v>0.01955263157894737</v>
       </c>
       <c r="O5">
-        <v>-2.299065420560748</v>
+        <v>0.5492996108949416</v>
       </c>
       <c r="P5">
-        <v>4.92</v>
+        <v>2.8234</v>
       </c>
       <c r="Q5">
-        <v>0.03277814790139907</v>
+        <v>0.01955263157894737</v>
       </c>
       <c r="R5">
-        <v>-2.299065420560748</v>
+        <v>0.5492996108949416</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1035,61 +1035,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>15.8</v>
+        <v>2.49</v>
       </c>
       <c r="V5">
-        <v>0.1052631578947369</v>
+        <v>0.01724376731301939</v>
       </c>
       <c r="W5">
-        <v>-0.01560904449307075</v>
+        <v>0.04155214227970897</v>
       </c>
       <c r="X5">
-        <v>0.08519247392634427</v>
+        <v>0.0762726690054274</v>
       </c>
       <c r="Y5">
-        <v>-0.100801518419415</v>
+        <v>-0.03472052672571842</v>
       </c>
       <c r="Z5">
-        <v>1.845916795069338</v>
+        <v>1.881046788263283</v>
       </c>
       <c r="AA5">
-        <v>-0.08351309707241912</v>
+        <v>0.0500396510705789</v>
       </c>
       <c r="AB5">
-        <v>0.08041085451991724</v>
+        <v>0.07262416477947153</v>
       </c>
       <c r="AC5">
-        <v>-0.1639239515923364</v>
+        <v>-0.02258451370889263</v>
       </c>
       <c r="AD5">
-        <v>18.2</v>
+        <v>19.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>18.2</v>
+        <v>19.1</v>
       </c>
       <c r="AG5">
-        <v>2.399999999999999</v>
+        <v>16.61</v>
       </c>
       <c r="AH5">
-        <v>0.1081402257872846</v>
+        <v>0.1168195718654434</v>
       </c>
       <c r="AI5">
-        <v>0.1282593375616631</v>
+        <v>0.1136904761904762</v>
       </c>
       <c r="AJ5">
-        <v>0.01573770491803278</v>
+        <v>0.1031612943295448</v>
       </c>
       <c r="AK5">
-        <v>0.01903251387787469</v>
+        <v>0.1003564739290677</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1.13</v>
+      </c>
+      <c r="AO5">
+        <v>5.584070796460177</v>
+      </c>
+      <c r="AQ5">
+        <v>5.584070796460177</v>
       </c>
     </row>
     <row r="6">
@@ -1108,125 +1114,104 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.344</v>
-      </c>
-      <c r="E6">
-        <v>0.0513</v>
-      </c>
       <c r="F6">
-        <v>0.644</v>
-      </c>
-      <c r="G6">
-        <v>0.06749358103005589</v>
-      </c>
-      <c r="H6">
-        <v>0.06749358103005589</v>
-      </c>
-      <c r="I6">
-        <v>-0.396654583899713</v>
-      </c>
-      <c r="J6">
-        <v>-0.396654583899713</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K6">
-        <v>1888.3</v>
-      </c>
-      <c r="L6">
-        <v>0.3564982631022504</v>
+        <v>-743.4</v>
       </c>
       <c r="M6">
-        <v>6865.5</v>
+        <v>1563.1</v>
       </c>
       <c r="N6">
-        <v>0.4605956110749579</v>
+        <v>0.1038059756008474</v>
       </c>
       <c r="O6">
-        <v>3.635809987819732</v>
+        <v>-2.102636534839925</v>
       </c>
       <c r="P6">
-        <v>1004.9</v>
+        <v>1139.9</v>
       </c>
       <c r="Q6">
-        <v>0.06741716256197293</v>
+        <v>0.07570112698317827</v>
       </c>
       <c r="R6">
-        <v>0.532171794736006</v>
+        <v>-1.533360236750067</v>
       </c>
       <c r="S6">
-        <v>5860.6</v>
+        <v>423.2</v>
       </c>
       <c r="T6">
-        <v>0.8536304711965625</v>
+        <v>0.2707440342908323</v>
       </c>
       <c r="U6">
-        <v>16700.9</v>
+        <v>25207.5</v>
       </c>
       <c r="V6">
-        <v>1.120437148205049</v>
+        <v>1.674038212499751</v>
       </c>
       <c r="W6">
-        <v>0.07604545893875446</v>
+        <v>-0.04385840707964601</v>
       </c>
       <c r="X6">
-        <v>0.09929414729141153</v>
+        <v>0.08704801730126338</v>
       </c>
       <c r="Y6">
-        <v>-0.02324868835265707</v>
+        <v>-0.1309064243809094</v>
       </c>
       <c r="Z6">
-        <v>0.2863119658812656</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0.1135669536921422</v>
+        <v>-0.1484049315554505</v>
       </c>
       <c r="AB6">
-        <v>0.07981867608123741</v>
+        <v>0.07100728957313095</v>
       </c>
       <c r="AC6">
-        <v>-0.1933856297733796</v>
+        <v>-0.2194122211285814</v>
       </c>
       <c r="AD6">
-        <v>8397.799999999999</v>
+        <v>8337.700000000001</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>8397.799999999999</v>
+        <v>8337.700000000001</v>
       </c>
       <c r="AG6">
-        <v>-8303.100000000002</v>
+        <v>-16869.8</v>
       </c>
       <c r="AH6">
-        <v>0.3603664685562254</v>
+        <v>0.3563789772435843</v>
       </c>
       <c r="AI6">
-        <v>0.3242769432752828</v>
+        <v>0.4028613948454306</v>
       </c>
       <c r="AJ6">
-        <v>-1.257550056038531</v>
+        <v>9.310557977813346</v>
       </c>
       <c r="AK6">
-        <v>-0.9028936179467387</v>
+        <v>3.739454259304414</v>
       </c>
       <c r="AL6">
-        <v>455.7</v>
+        <v>485.4</v>
       </c>
       <c r="AM6">
-        <v>455.7</v>
+        <v>485.4</v>
       </c>
       <c r="AN6">
-        <v>-4.410377606218161</v>
+        <v>-10.61586452762923</v>
       </c>
       <c r="AO6">
-        <v>-4.610489357033136</v>
+        <v>-2.068191182529872</v>
       </c>
       <c r="AP6">
-        <v>4.360642823381126</v>
+        <v>21.47924624395213</v>
       </c>
       <c r="AQ6">
-        <v>-4.610489357033136</v>
+        <v>-2.068191182529872</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0248</v>
+        <v>0.00114</v>
       </c>
       <c r="E2">
-        <v>0.127</v>
+        <v>-0.109</v>
       </c>
       <c r="F2">
-        <v>0.098</v>
+        <v>0.111</v>
       </c>
       <c r="G2">
-        <v>0.06021565742604924</v>
+        <v>0.1461615058542135</v>
       </c>
       <c r="H2">
-        <v>0.06021565742604924</v>
+        <v>0.1461615058542135</v>
       </c>
       <c r="I2">
-        <v>0.1133332133786206</v>
+        <v>0.1419884719072883</v>
       </c>
       <c r="J2">
-        <v>0.1082301125412904</v>
+        <v>0.1246577388905387</v>
       </c>
       <c r="K2">
-        <v>200.54</v>
+        <v>761.0999999999999</v>
       </c>
       <c r="L2">
-        <v>0.01941110422796965</v>
+        <v>0.01928431891717954</v>
       </c>
       <c r="M2">
-        <v>3186.9234</v>
+        <v>2710.4</v>
       </c>
       <c r="N2">
-        <v>0.07893895273952245</v>
+        <v>0.05723311344420701</v>
       </c>
       <c r="O2">
-        <v>15.89170938466141</v>
+        <v>3.561161476809881</v>
       </c>
       <c r="P2">
-        <v>1496.7234</v>
+        <v>1538.7</v>
       </c>
       <c r="Q2">
-        <v>0.03707330327950065</v>
+        <v>0.03249136350966696</v>
       </c>
       <c r="R2">
-        <v>7.463465642764535</v>
+        <v>2.02167914860071</v>
       </c>
       <c r="S2">
-        <v>1690.2</v>
+        <v>1171.7</v>
       </c>
       <c r="T2">
-        <v>0.5303547615860488</v>
+        <v>0.4322978158205431</v>
       </c>
       <c r="U2">
-        <v>26691.59</v>
+        <v>22904.3</v>
       </c>
       <c r="V2">
-        <v>0.6611411374219757</v>
+        <v>0.4836497934844121</v>
       </c>
       <c r="W2">
-        <v>-0.001153132399968521</v>
+        <v>-0.0767268862911796</v>
       </c>
       <c r="X2">
-        <v>0.08299400786832897</v>
+        <v>0.09007062766893106</v>
       </c>
       <c r="Y2">
-        <v>-0.08414714026829749</v>
+        <v>-0.1667975139601107</v>
       </c>
       <c r="Z2">
-        <v>0.903502648967011</v>
+        <v>8.502783195388229</v>
       </c>
       <c r="AA2">
-        <v>0.064807922920321</v>
+        <v>0.5513918836650273</v>
       </c>
       <c r="AB2">
-        <v>0.07244336912586012</v>
+        <v>0.07663334867379767</v>
       </c>
       <c r="AC2">
-        <v>-0.01843835534510071</v>
+        <v>0.4747585349912297</v>
       </c>
       <c r="AD2">
-        <v>14683.4</v>
+        <v>14256</v>
       </c>
       <c r="AE2">
-        <v>670.7095297139741</v>
+        <v>641.991913467395</v>
       </c>
       <c r="AF2">
-        <v>15354.10952971397</v>
+        <v>14897.99191346739</v>
       </c>
       <c r="AG2">
-        <v>-11337.48047028603</v>
+        <v>-8006.308086532605</v>
       </c>
       <c r="AH2">
-        <v>0.2755281080859761</v>
+        <v>0.2393052122331435</v>
       </c>
       <c r="AI2">
-        <v>0.4070018913529887</v>
+        <v>0.4309939478778361</v>
       </c>
       <c r="AJ2">
-        <v>-0.3904827995752859</v>
+        <v>-0.2034593803906269</v>
       </c>
       <c r="AK2">
-        <v>-1.027567491338659</v>
+        <v>-0.6865124064753577</v>
       </c>
       <c r="AL2">
-        <v>765.63</v>
+        <v>801.6</v>
       </c>
       <c r="AM2">
-        <v>765.63</v>
+        <v>801.6</v>
       </c>
       <c r="AN2">
-        <v>7.222528283325136</v>
+        <v>2.282055386585561</v>
       </c>
       <c r="AO2">
-        <v>1.511186865718428</v>
+        <v>6.967689620758483</v>
       </c>
       <c r="AP2">
-        <v>-5.576724284449594</v>
+        <v>-1.281624473592541</v>
       </c>
       <c r="AQ2">
-        <v>1.511186865718428</v>
+        <v>6.967689620758483</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Willis Towers Watson Public Limited Company (NasdaqGS:WTW)</t>
+          <t>Aviva plc (LSE:AV.)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0248</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="E3">
-        <v>0.127</v>
+        <v>-0.109</v>
       </c>
       <c r="F3">
-        <v>0.112</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2438919384350447</v>
+        <v>0.1132303606374056</v>
       </c>
       <c r="H3">
-        <v>0.2438919384350447</v>
+        <v>0.1132303606374056</v>
       </c>
       <c r="I3">
-        <v>0.2257946500976434</v>
+        <v>0.1172106513838412</v>
       </c>
       <c r="J3">
-        <v>0.1851268587723044</v>
+        <v>0.07429139578725233</v>
       </c>
       <c r="K3">
-        <v>1021</v>
+        <v>1673.3</v>
       </c>
       <c r="L3">
-        <v>0.1098912926487999</v>
+        <v>0.05847428012300811</v>
       </c>
       <c r="M3">
-        <v>1621</v>
+        <v>1621.4</v>
       </c>
       <c r="N3">
-        <v>0.06508367327273311</v>
+        <v>0.103997229135131</v>
       </c>
       <c r="O3">
-        <v>1.587659157688541</v>
+        <v>0.9689834458853763</v>
       </c>
       <c r="P3">
-        <v>354</v>
+        <v>1186.7</v>
       </c>
       <c r="Q3">
-        <v>0.01421321427424276</v>
+        <v>0.07611540139056368</v>
       </c>
       <c r="R3">
-        <v>0.346718903036239</v>
+        <v>0.7091973943704059</v>
       </c>
       <c r="S3">
-        <v>1267</v>
+        <v>434.7</v>
       </c>
       <c r="T3">
-        <v>0.7816162862430598</v>
+        <v>0.2681016405575429</v>
       </c>
       <c r="U3">
-        <v>1247</v>
+        <v>21418.7</v>
       </c>
       <c r="V3">
-        <v>0.05006745254231844</v>
+        <v>1.373803781717423</v>
       </c>
       <c r="W3">
-        <v>0.1037812563529173</v>
+        <v>0.1429523378298719</v>
       </c>
       <c r="X3">
-        <v>0.07893999843539458</v>
+        <v>0.09007062766893106</v>
       </c>
       <c r="Y3">
-        <v>0.02484125791752267</v>
-      </c>
-      <c r="Z3">
-        <v>2.540808867781942</v>
-      </c>
-      <c r="AA3">
-        <v>0.4703719644332862</v>
+        <v>0.05288171016094087</v>
       </c>
       <c r="AB3">
-        <v>0.07226257347224871</v>
-      </c>
-      <c r="AC3">
-        <v>0.3981093909610375</v>
+        <v>0.07482631070142012</v>
       </c>
       <c r="AD3">
-        <v>5222</v>
+        <v>8016.2</v>
       </c>
       <c r="AE3">
-        <v>670.7095297139741</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>5892.709529713974</v>
+        <v>8016.2</v>
       </c>
       <c r="AG3">
-        <v>4645.709529713974</v>
+        <v>-13402.5</v>
       </c>
       <c r="AH3">
-        <v>0.1913272695117656</v>
+        <v>0.3395687719744144</v>
       </c>
       <c r="AI3">
-        <v>0.383198129625718</v>
+        <v>0.4015066139752471</v>
       </c>
       <c r="AJ3">
-        <v>0.1572039899568868</v>
+        <v>-6.124617282822284</v>
       </c>
       <c r="AK3">
-        <v>0.3287668973695201</v>
+        <v>9.221480666024497</v>
       </c>
       <c r="AL3">
-        <v>226</v>
+        <v>487.8</v>
       </c>
       <c r="AM3">
-        <v>226</v>
+        <v>487.8</v>
       </c>
       <c r="AN3">
-        <v>1.922680412371134</v>
+        <v>2.37046455924535</v>
       </c>
       <c r="AO3">
-        <v>9.221238938053098</v>
+        <v>6.875973759737597</v>
       </c>
       <c r="AP3">
-        <v>1.710496881337987</v>
+        <v>-3.963243339148949</v>
       </c>
       <c r="AQ3">
-        <v>9.221238938053098</v>
+        <v>6.875973759737597</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saga plc (LSE:SAGA)</t>
+          <t>Willis Towers Watson Public Limited Company (NasdaqGS:WTW)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,115 +853,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0629</v>
+        <v>0.0238</v>
+      </c>
+      <c r="F4">
+        <v>0.111</v>
       </c>
       <c r="G4">
-        <v>0.1344956413449564</v>
+        <v>0.2470180446528698</v>
       </c>
       <c r="H4">
-        <v>0.1344956413449564</v>
+        <v>0.2470180446528698</v>
       </c>
       <c r="I4">
-        <v>0.08792029887920298</v>
+        <v>0.2183302698854645</v>
       </c>
       <c r="J4">
-        <v>0.08792029887920298</v>
+        <v>0.2183302698854645</v>
       </c>
       <c r="K4">
-        <v>-82.2</v>
+        <v>-722</v>
       </c>
       <c r="L4">
-        <v>-0.1023661270236613</v>
+        <v>-0.07360587215822204</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1089</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.03451532746773498</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-1.508310249307479</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>352</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.0111564694845204</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0.4875346260387812</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>737</v>
+      </c>
+      <c r="T4">
+        <v>0.6767676767676768</v>
       </c>
       <c r="U4">
-        <v>234.6</v>
+        <v>1372</v>
       </c>
       <c r="V4">
-        <v>0.8909988606152677</v>
+        <v>0.04348487537716474</v>
       </c>
       <c r="W4">
-        <v>-0.1702921068986948</v>
+        <v>-0.0767268862911796</v>
       </c>
       <c r="X4">
-        <v>0.1801542354546815</v>
+        <v>0.08227119046042727</v>
       </c>
       <c r="Y4">
-        <v>-0.3504463423533763</v>
+        <v>-0.1589980767516069</v>
       </c>
       <c r="Z4">
-        <v>0.9050946798917944</v>
+        <v>2.525494444514204</v>
       </c>
       <c r="AA4">
-        <v>0.07957619477006311</v>
+        <v>0.5513918836650273</v>
       </c>
       <c r="AB4">
-        <v>0.0938683917513719</v>
+        <v>0.07663334867379767</v>
       </c>
       <c r="AC4">
-        <v>-0.01429219698130879</v>
+        <v>0.4747585349912297</v>
       </c>
       <c r="AD4">
-        <v>1104.6</v>
+        <v>5311</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>641.991913467395</v>
       </c>
       <c r="AF4">
-        <v>1104.6</v>
+        <v>5952.991913467395</v>
       </c>
       <c r="AG4">
-        <v>869.9999999999999</v>
+        <v>4580.991913467395</v>
       </c>
       <c r="AH4">
-        <v>0.8075151692375174</v>
+        <v>0.1587287076389381</v>
       </c>
       <c r="AI4">
-        <v>0.7448415374241402</v>
+        <v>0.4402126357510336</v>
       </c>
       <c r="AJ4">
-        <v>0.7676696373422747</v>
+        <v>0.126784224008285</v>
       </c>
       <c r="AK4">
-        <v>0.6968920217878884</v>
+        <v>0.3770055931310523</v>
       </c>
       <c r="AL4">
-        <v>53.1</v>
+        <v>260</v>
       </c>
       <c r="AM4">
-        <v>53.1</v>
+        <v>260</v>
       </c>
       <c r="AN4">
-        <v>10.787109375</v>
+        <v>1.946847507331378</v>
       </c>
       <c r="AO4">
-        <v>1.329566854990584</v>
+        <v>8.165384615384616</v>
       </c>
       <c r="AP4">
-        <v>8.496093749999998</v>
+        <v>1.679249235142007</v>
       </c>
       <c r="AQ4">
-        <v>1.329566854990584</v>
+        <v>8.165384615384616</v>
       </c>
     </row>
     <row r="5">
@@ -981,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Helios Underwriting plc (AIM:HUW)</t>
+          <t>Saga plc (LSE:SAGA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -990,228 +987,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.436</v>
+        <v>0.00114</v>
+      </c>
+      <c r="F5">
+        <v>0.481</v>
       </c>
       <c r="G5">
+        <v>0.1011225175093543</v>
+      </c>
+      <c r="H5">
+        <v>0.1011225175093543</v>
+      </c>
+      <c r="I5">
+        <v>0.1038088841984074</v>
+      </c>
+      <c r="J5">
+        <v>0.1038088841984074</v>
+      </c>
+      <c r="K5">
+        <v>-190.2</v>
+      </c>
+      <c r="L5">
+        <v>-0.1824810515206754</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
         <v>0</v>
       </c>
-      <c r="H5">
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
         <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0.02660202360876897</v>
-      </c>
-      <c r="J5">
-        <v>0.02660202360876897</v>
-      </c>
-      <c r="K5">
-        <v>5.14</v>
-      </c>
-      <c r="L5">
-        <v>0.02166947723440135</v>
-      </c>
-      <c r="M5">
-        <v>2.8234</v>
-      </c>
-      <c r="N5">
-        <v>0.01955263157894737</v>
-      </c>
-      <c r="O5">
-        <v>0.5492996108949416</v>
-      </c>
-      <c r="P5">
-        <v>2.8234</v>
-      </c>
-      <c r="Q5">
-        <v>0.01955263157894737</v>
-      </c>
-      <c r="R5">
-        <v>0.5492996108949416</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>2.49</v>
+        <v>113.6</v>
       </c>
       <c r="V5">
-        <v>0.01724376731301939</v>
+        <v>0.5278810408921933</v>
       </c>
       <c r="W5">
-        <v>0.04155214227970897</v>
+        <v>-0.5026427061310782</v>
       </c>
       <c r="X5">
-        <v>0.0762726690054274</v>
+        <v>0.1811718425874514</v>
       </c>
       <c r="Y5">
-        <v>-0.03472052672571842</v>
+        <v>-0.6838145487185296</v>
       </c>
       <c r="Z5">
-        <v>1.881046788263283</v>
+        <v>1.375610399894417</v>
       </c>
       <c r="AA5">
-        <v>0.0500396510705789</v>
+        <v>0.1428005807047644</v>
       </c>
       <c r="AB5">
-        <v>0.07262416477947153</v>
+        <v>0.09249792630414405</v>
       </c>
       <c r="AC5">
-        <v>-0.02258451370889263</v>
+        <v>0.05030265440062037</v>
       </c>
       <c r="AD5">
-        <v>19.1</v>
+        <v>928.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>19.1</v>
+        <v>928.8</v>
       </c>
       <c r="AG5">
-        <v>16.61</v>
+        <v>815.1999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.1168195718654434</v>
+        <v>0.8118881118881118</v>
       </c>
       <c r="AI5">
-        <v>0.1136904761904762</v>
+        <v>0.8613558378929796</v>
       </c>
       <c r="AJ5">
-        <v>0.1031612943295448</v>
+        <v>0.7911490683229814</v>
       </c>
       <c r="AK5">
-        <v>0.1003564739290677</v>
+        <v>0.8450295428630662</v>
       </c>
       <c r="AL5">
-        <v>1.13</v>
+        <v>53.8</v>
       </c>
       <c r="AM5">
-        <v>1.13</v>
+        <v>53.8</v>
+      </c>
+      <c r="AN5">
+        <v>6.76474872541879</v>
       </c>
       <c r="AO5">
-        <v>5.584070796460177</v>
+        <v>2.011152416356877</v>
+      </c>
+      <c r="AP5">
+        <v>5.937363437727603</v>
       </c>
       <c r="AQ5">
-        <v>5.584070796460177</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Aviva plc (LSE:AV.)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="F6">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="K6">
-        <v>-743.4</v>
-      </c>
-      <c r="M6">
-        <v>1563.1</v>
-      </c>
-      <c r="N6">
-        <v>0.1038059756008474</v>
-      </c>
-      <c r="O6">
-        <v>-2.102636534839925</v>
-      </c>
-      <c r="P6">
-        <v>1139.9</v>
-      </c>
-      <c r="Q6">
-        <v>0.07570112698317827</v>
-      </c>
-      <c r="R6">
-        <v>-1.533360236750067</v>
-      </c>
-      <c r="S6">
-        <v>423.2</v>
-      </c>
-      <c r="T6">
-        <v>0.2707440342908323</v>
-      </c>
-      <c r="U6">
-        <v>25207.5</v>
-      </c>
-      <c r="V6">
-        <v>1.674038212499751</v>
-      </c>
-      <c r="W6">
-        <v>-0.04385840707964601</v>
-      </c>
-      <c r="X6">
-        <v>0.08704801730126338</v>
-      </c>
-      <c r="Y6">
-        <v>-0.1309064243809094</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>-0.1484049315554505</v>
-      </c>
-      <c r="AB6">
-        <v>0.07100728957313095</v>
-      </c>
-      <c r="AC6">
-        <v>-0.2194122211285814</v>
-      </c>
-      <c r="AD6">
-        <v>8337.700000000001</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>8337.700000000001</v>
-      </c>
-      <c r="AG6">
-        <v>-16869.8</v>
-      </c>
-      <c r="AH6">
-        <v>0.3563789772435843</v>
-      </c>
-      <c r="AI6">
-        <v>0.4028613948454306</v>
-      </c>
-      <c r="AJ6">
-        <v>9.310557977813346</v>
-      </c>
-      <c r="AK6">
-        <v>3.739454259304414</v>
-      </c>
-      <c r="AL6">
-        <v>485.4</v>
-      </c>
-      <c r="AM6">
-        <v>485.4</v>
-      </c>
-      <c r="AN6">
-        <v>-10.61586452762923</v>
-      </c>
-      <c r="AO6">
-        <v>-2.068191182529872</v>
-      </c>
-      <c r="AP6">
-        <v>21.47924624395213</v>
-      </c>
-      <c r="AQ6">
-        <v>-2.068191182529872</v>
+        <v>2.011152416356877</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00114</v>
+        <v>0.0238</v>
       </c>
       <c r="E2">
-        <v>-0.109</v>
+        <v>0.8059999999999999</v>
       </c>
       <c r="F2">
-        <v>0.111</v>
+        <v>0.199</v>
       </c>
       <c r="G2">
-        <v>0.1461615058542135</v>
+        <v>0.2263016101748011</v>
       </c>
       <c r="H2">
-        <v>0.1461615058542135</v>
+        <v>0.2263016101748011</v>
       </c>
       <c r="I2">
-        <v>0.1419884719072883</v>
+        <v>0.2041584950196927</v>
       </c>
       <c r="J2">
-        <v>0.1246577388905387</v>
+        <v>0.1885367453435009</v>
       </c>
       <c r="K2">
-        <v>761.0999999999999</v>
+        <v>-889.8</v>
       </c>
       <c r="L2">
-        <v>0.01928431891717954</v>
+        <v>-0.07964055241794731</v>
       </c>
       <c r="M2">
-        <v>2710.4</v>
+        <v>1097.01</v>
       </c>
       <c r="N2">
-        <v>0.05723311344420701</v>
+        <v>0.03427256595143775</v>
       </c>
       <c r="O2">
-        <v>3.561161476809881</v>
+        <v>-1.232872555630479</v>
       </c>
       <c r="P2">
-        <v>1538.7</v>
+        <v>354.93</v>
       </c>
       <c r="Q2">
-        <v>0.03249136350966696</v>
+        <v>0.01108865172892116</v>
       </c>
       <c r="R2">
-        <v>2.02167914860071</v>
+        <v>-0.3988873904248146</v>
       </c>
       <c r="S2">
-        <v>1171.7</v>
+        <v>742.08</v>
       </c>
       <c r="T2">
-        <v>0.4322978158205431</v>
+        <v>0.6764569147045151</v>
       </c>
       <c r="U2">
-        <v>22904.3</v>
+        <v>1530.5</v>
       </c>
       <c r="V2">
-        <v>0.4836497934844121</v>
+        <v>0.04781557341197935</v>
       </c>
       <c r="W2">
         <v>-0.0767268862911796</v>
       </c>
       <c r="X2">
-        <v>0.09007062766893106</v>
+        <v>0.08517781416049544</v>
       </c>
       <c r="Y2">
-        <v>-0.1667975139601107</v>
+        <v>-0.161904700451675</v>
       </c>
       <c r="Z2">
-        <v>8.502783195388229</v>
+        <v>2.324158668829706</v>
       </c>
       <c r="AA2">
-        <v>0.5513918836650273</v>
+        <v>0.1452355636779041</v>
       </c>
       <c r="AB2">
-        <v>0.07663334867379767</v>
+        <v>0.07661901980000022</v>
       </c>
       <c r="AC2">
-        <v>0.4747585349912297</v>
+        <v>0.06936300312744119</v>
       </c>
       <c r="AD2">
-        <v>14256</v>
+        <v>6315</v>
       </c>
       <c r="AE2">
         <v>641.991913467395</v>
       </c>
       <c r="AF2">
-        <v>14897.99191346739</v>
+        <v>6956.991913467395</v>
       </c>
       <c r="AG2">
-        <v>-8006.308086532605</v>
+        <v>5426.491913467395</v>
       </c>
       <c r="AH2">
-        <v>0.2393052122331435</v>
+        <v>0.1785428446072652</v>
       </c>
       <c r="AI2">
-        <v>0.4309939478778361</v>
+        <v>0.4683552487755828</v>
       </c>
       <c r="AJ2">
-        <v>-0.2034593803906269</v>
+        <v>0.1449581295976759</v>
       </c>
       <c r="AK2">
-        <v>-0.6865124064753577</v>
+        <v>0.4072844581784537</v>
       </c>
       <c r="AL2">
-        <v>801.6</v>
+        <v>315.97</v>
       </c>
       <c r="AM2">
-        <v>801.6</v>
+        <v>315.97</v>
       </c>
       <c r="AN2">
-        <v>2.282055386585561</v>
+        <v>2.203957700764318</v>
       </c>
       <c r="AO2">
-        <v>6.967689620758483</v>
+        <v>7.160173434186791</v>
       </c>
       <c r="AP2">
-        <v>-1.281624473592541</v>
+        <v>1.893865184611522</v>
       </c>
       <c r="AQ2">
-        <v>6.967689620758483</v>
+        <v>7.160173434186791</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aviva plc (LSE:AV.)</t>
+          <t>Willis Towers Watson Public Limited Company (NasdaqGS:WTW)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,115 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.09130000000000001</v>
-      </c>
-      <c r="E3">
-        <v>-0.109</v>
+        <v>0.0238</v>
       </c>
       <c r="F3">
-        <v>0.09429999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="G3">
-        <v>0.1132303606374056</v>
+        <v>0.2470180446528698</v>
       </c>
       <c r="H3">
-        <v>0.1132303606374056</v>
+        <v>0.2470180446528698</v>
       </c>
       <c r="I3">
-        <v>0.1172106513838412</v>
+        <v>0.2183302698854645</v>
       </c>
       <c r="J3">
-        <v>0.07429139578725233</v>
+        <v>0.2183302698854645</v>
       </c>
       <c r="K3">
-        <v>1673.3</v>
+        <v>-722</v>
       </c>
       <c r="L3">
-        <v>0.05847428012300811</v>
+        <v>-0.07360587215822204</v>
       </c>
       <c r="M3">
-        <v>1621.4</v>
+        <v>1089</v>
       </c>
       <c r="N3">
-        <v>0.103997229135131</v>
+        <v>0.03451532746773498</v>
       </c>
       <c r="O3">
-        <v>0.9689834458853763</v>
+        <v>-1.508310249307479</v>
       </c>
       <c r="P3">
-        <v>1186.7</v>
+        <v>352</v>
       </c>
       <c r="Q3">
-        <v>0.07611540139056368</v>
+        <v>0.0111564694845204</v>
       </c>
       <c r="R3">
-        <v>0.7091973943704059</v>
+        <v>-0.4875346260387812</v>
       </c>
       <c r="S3">
-        <v>434.7</v>
+        <v>737</v>
       </c>
       <c r="T3">
-        <v>0.2681016405575429</v>
+        <v>0.6767676767676768</v>
       </c>
       <c r="U3">
-        <v>21418.7</v>
+        <v>1372</v>
       </c>
       <c r="V3">
-        <v>1.373803781717423</v>
+        <v>0.04348487537716474</v>
       </c>
       <c r="W3">
-        <v>0.1429523378298719</v>
+        <v>-0.0767268862911796</v>
       </c>
       <c r="X3">
-        <v>0.09007062766893106</v>
+        <v>0.08225415805491484</v>
       </c>
       <c r="Y3">
-        <v>0.05288171016094087</v>
+        <v>-0.1589810443460944</v>
+      </c>
+      <c r="Z3">
+        <v>2.525494444514204</v>
+      </c>
+      <c r="AA3">
+        <v>0.5513918836650273</v>
       </c>
       <c r="AB3">
-        <v>0.07482631070142012</v>
+        <v>0.07661901980000022</v>
+      </c>
+      <c r="AC3">
+        <v>0.4747728638650272</v>
       </c>
       <c r="AD3">
-        <v>8016.2</v>
+        <v>5311</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>641.991913467395</v>
       </c>
       <c r="AF3">
-        <v>8016.2</v>
+        <v>5952.991913467395</v>
       </c>
       <c r="AG3">
-        <v>-13402.5</v>
+        <v>4580.991913467395</v>
       </c>
       <c r="AH3">
-        <v>0.3395687719744144</v>
+        <v>0.1587287076389381</v>
       </c>
       <c r="AI3">
-        <v>0.4015066139752471</v>
+        <v>0.4402126357510336</v>
       </c>
       <c r="AJ3">
-        <v>-6.124617282822284</v>
+        <v>0.126784224008285</v>
       </c>
       <c r="AK3">
-        <v>9.221480666024497</v>
+        <v>0.3770055931310523</v>
       </c>
       <c r="AL3">
-        <v>487.8</v>
+        <v>260</v>
       </c>
       <c r="AM3">
-        <v>487.8</v>
+        <v>260</v>
       </c>
       <c r="AN3">
-        <v>2.37046455924535</v>
+        <v>1.946847507331378</v>
       </c>
       <c r="AO3">
-        <v>6.875973759737597</v>
+        <v>8.165384615384616</v>
       </c>
       <c r="AP3">
-        <v>-3.963243339148949</v>
+        <v>1.679249235142007</v>
       </c>
       <c r="AQ3">
-        <v>6.875973759737597</v>
+        <v>8.165384615384616</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson Public Limited Company (NasdaqGS:WTW)</t>
+          <t>Helios Underwriting plc (AIM:HUW)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,121 +859,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0238</v>
+        <v>0.46</v>
+      </c>
+      <c r="E4">
+        <v>0.8059999999999999</v>
       </c>
       <c r="F4">
-        <v>0.111</v>
+        <v>0.199</v>
       </c>
       <c r="G4">
-        <v>0.2470180446528698</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>0.2470180446528698</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.2183302698854645</v>
+        <v>0.09707529558182951</v>
       </c>
       <c r="J4">
-        <v>0.2183302698854645</v>
+        <v>0.07479134456854357</v>
       </c>
       <c r="K4">
-        <v>-722</v>
+        <v>22.4</v>
       </c>
       <c r="L4">
-        <v>-0.07360587215822204</v>
+        <v>0.06969508400746734</v>
       </c>
       <c r="M4">
-        <v>1089</v>
+        <v>8.01</v>
       </c>
       <c r="N4">
-        <v>0.03451532746773498</v>
+        <v>0.03309917355371901</v>
       </c>
       <c r="O4">
-        <v>-1.508310249307479</v>
+        <v>0.3575892857142857</v>
       </c>
       <c r="P4">
-        <v>352</v>
+        <v>2.93</v>
       </c>
       <c r="Q4">
-        <v>0.0111564694845204</v>
+        <v>0.01210743801652893</v>
       </c>
       <c r="R4">
-        <v>-0.4875346260387812</v>
+        <v>0.1308035714285714</v>
       </c>
       <c r="S4">
-        <v>737</v>
+        <v>5.08</v>
       </c>
       <c r="T4">
-        <v>0.6767676767676768</v>
+        <v>0.634207240948814</v>
       </c>
       <c r="U4">
-        <v>1372</v>
+        <v>44.9</v>
       </c>
       <c r="V4">
-        <v>0.04348487537716474</v>
+        <v>0.1855371900826446</v>
       </c>
       <c r="W4">
-        <v>-0.0767268862911796</v>
+        <v>0.1504365345869711</v>
       </c>
       <c r="X4">
-        <v>0.08227119046042727</v>
+        <v>0.08517781416049544</v>
       </c>
       <c r="Y4">
-        <v>-0.1589980767516069</v>
+        <v>0.06525872042647565</v>
       </c>
       <c r="Z4">
-        <v>2.525494444514204</v>
+        <v>1.941876623768956</v>
       </c>
       <c r="AA4">
-        <v>0.5513918836650273</v>
+        <v>0.1452355636779041</v>
       </c>
       <c r="AB4">
-        <v>0.07663334867379767</v>
+        <v>0.07587256055046286</v>
       </c>
       <c r="AC4">
-        <v>0.4747585349912297</v>
+        <v>0.06936300312744119</v>
       </c>
       <c r="AD4">
-        <v>5311</v>
+        <v>75.2</v>
       </c>
       <c r="AE4">
-        <v>641.991913467395</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>5952.991913467395</v>
+        <v>75.2</v>
       </c>
       <c r="AG4">
-        <v>4580.991913467395</v>
+        <v>30.3</v>
       </c>
       <c r="AH4">
-        <v>0.1587287076389381</v>
+        <v>0.2370744010088273</v>
       </c>
       <c r="AI4">
-        <v>0.4402126357510336</v>
+        <v>0.2974683544303797</v>
       </c>
       <c r="AJ4">
-        <v>0.126784224008285</v>
+        <v>0.1112743297833272</v>
       </c>
       <c r="AK4">
-        <v>0.3770055931310523</v>
+        <v>0.1457431457431458</v>
       </c>
       <c r="AL4">
-        <v>260</v>
+        <v>2.17</v>
       </c>
       <c r="AM4">
-        <v>260</v>
-      </c>
-      <c r="AN4">
-        <v>1.946847507331378</v>
+        <v>2.17</v>
       </c>
       <c r="AO4">
-        <v>8.165384615384616</v>
-      </c>
-      <c r="AP4">
-        <v>1.679249235142007</v>
+        <v>14.3778801843318</v>
       </c>
       <c r="AQ4">
-        <v>8.165384615384616</v>
+        <v>14.3778801843318</v>
       </c>
     </row>
     <row r="5">
@@ -1041,10 +1044,10 @@
         <v>-0.5026427061310782</v>
       </c>
       <c r="X5">
-        <v>0.1811718425874514</v>
+        <v>0.1811086226023397</v>
       </c>
       <c r="Y5">
-        <v>-0.6838145487185296</v>
+        <v>-0.6837513287334179</v>
       </c>
       <c r="Z5">
         <v>1.375610399894417</v>
@@ -1053,10 +1056,10 @@
         <v>0.1428005807047644</v>
       </c>
       <c r="AB5">
-        <v>0.09249792630414405</v>
+        <v>0.09248603387337828</v>
       </c>
       <c r="AC5">
-        <v>0.05030265440062037</v>
+        <v>0.05031454683138614</v>
       </c>
       <c r="AD5">
         <v>928.8</v>
